--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_nuble.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_nuble.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.31508027522936</v>
+      </c>
+      <c r="C2">
         <v>32.5043004587156</v>
-      </c>
-      <c r="C2">
-        <v>27.31508027522936</v>
       </c>
       <c r="D2">
         <v>3.07651598676957</v>
       </c>
       <c r="E2">
+        <v>17.091218943403</v>
+      </c>
+      <c r="F2">
+        <v>62.57063413759081</v>
+      </c>
+      <c r="G2">
         <v>20.33814691900619</v>
-      </c>
-      <c r="F2">
-        <v>62.57063413759082</v>
-      </c>
-      <c r="G2">
-        <v>17.091218943403</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>29.90121051899262</v>
+      </c>
+      <c r="C3">
         <v>39.43230833449284</v>
-      </c>
-      <c r="C3">
-        <v>29.90121051899262</v>
       </c>
       <c r="D3">
         <v>2.535991531404375</v>
       </c>
       <c r="E3">
-        <v>23.28677074774034</v>
+        <v>17.658175842235</v>
       </c>
       <c r="F3">
         <v>59.05505341002465</v>
       </c>
       <c r="G3">
-        <v>17.658175842235</v>
+        <v>23.28677074774034</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>27.96253563187186</v>
+      </c>
+      <c r="C4">
         <v>26.05764445047735</v>
-      </c>
-      <c r="C4">
-        <v>27.96253563187186</v>
       </c>
       <c r="D4">
         <v>3.837645424552874</v>
       </c>
       <c r="E4">
-        <v>16.91833137485311</v>
+        <v>18.1551116333725</v>
       </c>
       <c r="F4">
         <v>64.92655699177439</v>
       </c>
       <c r="G4">
-        <v>18.1551116333725</v>
+        <v>16.91833137485311</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>28.05914972273568</v>
+      </c>
+      <c r="C5">
         <v>39.211337030191</v>
-      </c>
-      <c r="C5">
-        <v>28.05914972273568</v>
       </c>
       <c r="D5">
         <v>2.550282840980516</v>
       </c>
       <c r="E5">
-        <v>23.44187417120967</v>
+        <v>16.77471636952998</v>
       </c>
       <c r="F5">
         <v>59.78340945926035</v>
       </c>
       <c r="G5">
-        <v>16.77471636952998</v>
+        <v>23.44187417120967</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.53971644979608</v>
+      </c>
+      <c r="C6">
         <v>38.70654496018644</v>
-      </c>
-      <c r="C6">
-        <v>29.53971644979608</v>
       </c>
       <c r="D6">
         <v>2.58354239839438</v>
       </c>
       <c r="E6">
-        <v>23.00588710608334</v>
+        <v>17.55742814267575</v>
       </c>
       <c r="F6">
         <v>59.4366847512409</v>
       </c>
       <c r="G6">
-        <v>17.55742814267575</v>
+        <v>23.00588710608334</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>25.76476167891866</v>
+      </c>
+      <c r="C7">
         <v>39.35262034621769</v>
-      </c>
-      <c r="C7">
-        <v>25.76476167891866</v>
       </c>
       <c r="D7">
         <v>2.541126845435372</v>
       </c>
       <c r="E7">
-        <v>23.83311790894729</v>
+        <v>15.6039063622002</v>
       </c>
       <c r="F7">
         <v>60.56297572885251</v>
       </c>
       <c r="G7">
-        <v>15.6039063622002</v>
+        <v>23.83311790894729</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.65140374331551</v>
+      </c>
+      <c r="C8">
         <v>44.93649732620321</v>
-      </c>
-      <c r="C8">
-        <v>28.65140374331551</v>
       </c>
       <c r="D8">
         <v>2.225362588322797</v>
       </c>
       <c r="E8">
-        <v>25.88688327316486</v>
+        <v>16.50541516245487</v>
       </c>
       <c r="F8">
         <v>57.60770156438026</v>
       </c>
       <c r="G8">
-        <v>16.50541516245487</v>
+        <v>25.88688327316486</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>28.54378818737271</v>
+      </c>
+      <c r="C9">
         <v>42.28105906313645</v>
-      </c>
-      <c r="C9">
-        <v>28.54378818737271</v>
       </c>
       <c r="D9">
         <v>2.365125240847784</v>
       </c>
       <c r="E9">
+        <v>16.70938897168405</v>
+      </c>
+      <c r="F9">
+        <v>58.53949329359166</v>
+      </c>
+      <c r="G9">
         <v>24.75111773472429</v>
-      </c>
-      <c r="F9">
-        <v>58.53949329359165</v>
-      </c>
-      <c r="G9">
-        <v>16.70938897168405</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.31769722814499</v>
+      </c>
+      <c r="C10">
         <v>39.68550106609808</v>
-      </c>
-      <c r="C10">
-        <v>29.31769722814499</v>
       </c>
       <c r="D10">
         <v>2.519811954331766</v>
       </c>
       <c r="E10">
-        <v>23.48210061504495</v>
+        <v>17.34742154234348</v>
       </c>
       <c r="F10">
         <v>59.17047784261158</v>
       </c>
       <c r="G10">
-        <v>17.34742154234348</v>
+        <v>23.48210061504495</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>27.00778941713672</v>
+      </c>
+      <c r="C11">
         <v>42.60005372011818</v>
-      </c>
-      <c r="C11">
-        <v>27.00778941713672</v>
       </c>
       <c r="D11">
         <v>2.347414880201765</v>
       </c>
       <c r="E11">
+        <v>15.92366774883205</v>
+      </c>
+      <c r="F11">
+        <v>58.95953757225433</v>
+      </c>
+      <c r="G11">
         <v>25.11679467891361</v>
-      </c>
-      <c r="F11">
-        <v>58.95953757225434</v>
-      </c>
-      <c r="G11">
-        <v>15.92366774883206</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>25.3998720409469</v>
+      </c>
+      <c r="C12">
         <v>53.51887396033269</v>
-      </c>
-      <c r="C12">
-        <v>25.3998720409469</v>
       </c>
       <c r="D12">
         <v>1.868499701135684</v>
       </c>
       <c r="E12">
-        <v>29.91239048811014</v>
+        <v>14.19631682460218</v>
       </c>
       <c r="F12">
         <v>55.89129268728769</v>
       </c>
       <c r="G12">
-        <v>14.19631682460218</v>
+        <v>29.91239048811014</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>27.38812193088113</v>
+      </c>
+      <c r="C13">
         <v>41.24895765774113</v>
-      </c>
-      <c r="C13">
-        <v>27.38812193088113</v>
       </c>
       <c r="D13">
         <v>2.424303683737646</v>
       </c>
       <c r="E13">
-        <v>24.46019449480798</v>
+        <v>16.24086588648975</v>
       </c>
       <c r="F13">
         <v>59.29893961870226</v>
       </c>
       <c r="G13">
-        <v>16.24086588648975</v>
+        <v>24.46019449480798</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>25.36775743020114</v>
+      </c>
+      <c r="C14">
         <v>49.4145902131492</v>
-      </c>
-      <c r="C14">
-        <v>25.36775743020114</v>
       </c>
       <c r="D14">
         <v>2.023693803159174</v>
       </c>
       <c r="E14">
-        <v>28.27207145310889</v>
+        <v>14.51391274476125</v>
       </c>
       <c r="F14">
-        <v>57.21401580212984</v>
+        <v>57.21401580212986</v>
       </c>
       <c r="G14">
-        <v>14.51391274476125</v>
+        <v>28.2720714531089</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>26.95035460992908</v>
+      </c>
+      <c r="C15">
         <v>50.41908446163765</v>
-      </c>
-      <c r="C15">
-        <v>26.95035460992908</v>
       </c>
       <c r="D15">
         <v>1.983375959079284</v>
       </c>
       <c r="E15">
-        <v>28.42602689930934</v>
+        <v>15.19447473645947</v>
       </c>
       <c r="F15">
         <v>56.3794983642312</v>
       </c>
       <c r="G15">
-        <v>15.19447473645947</v>
+        <v>28.42602689930934</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>33.15677966101695</v>
+      </c>
+      <c r="C16">
         <v>35.38135593220339</v>
-      </c>
-      <c r="C16">
-        <v>33.15677966101695</v>
       </c>
       <c r="D16">
         <v>2.826347305389222</v>
       </c>
       <c r="E16">
+        <v>19.67316153362665</v>
+      </c>
+      <c r="F16">
+        <v>59.33375235700818</v>
+      </c>
+      <c r="G16">
         <v>20.99308610936518</v>
-      </c>
-      <c r="F16">
-        <v>59.33375235700817</v>
-      </c>
-      <c r="G16">
-        <v>19.67316153362665</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>29.477858559154</v>
+      </c>
+      <c r="C17">
         <v>45.27428949107733</v>
-      </c>
-      <c r="C17">
-        <v>29.477858559154</v>
       </c>
       <c r="D17">
         <v>2.208759124087591</v>
       </c>
       <c r="E17">
-        <v>25.90771558245084</v>
+        <v>16.86838124054463</v>
       </c>
       <c r="F17">
         <v>57.22390317700454</v>
       </c>
       <c r="G17">
-        <v>16.86838124054463</v>
+        <v>25.90771558245084</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>27.83440039045678</v>
+      </c>
+      <c r="C18">
         <v>38.43415348396543</v>
-      </c>
-      <c r="C18">
-        <v>27.83440039045678</v>
       </c>
       <c r="D18">
         <v>2.601852543512363</v>
       </c>
       <c r="E18">
-        <v>23.11570804482586</v>
+        <v>16.74062818365479</v>
       </c>
       <c r="F18">
         <v>60.14366377151935</v>
       </c>
       <c r="G18">
-        <v>16.74062818365479</v>
+        <v>23.11570804482586</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>29.64418128493166</v>
+      </c>
+      <c r="C19">
         <v>32.18969619832881</v>
-      </c>
-      <c r="C19">
-        <v>29.64418128493166</v>
       </c>
       <c r="D19">
         <v>3.10658414990545</v>
       </c>
       <c r="E19">
-        <v>19.89057958625406</v>
+        <v>18.31766113865618</v>
       </c>
       <c r="F19">
         <v>61.79175927508976</v>
       </c>
       <c r="G19">
-        <v>18.31766113865618</v>
+        <v>19.89057958625406</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>29.28767123287671</v>
+      </c>
+      <c r="C20">
         <v>22.43835616438356</v>
-      </c>
-      <c r="C20">
-        <v>29.28767123287671</v>
       </c>
       <c r="D20">
         <v>4.456654456654457</v>
       </c>
       <c r="E20">
-        <v>14.7887323943662</v>
+        <v>19.30299747201155</v>
       </c>
       <c r="F20">
         <v>65.90827013362224</v>
       </c>
       <c r="G20">
-        <v>19.30299747201155</v>
+        <v>14.7887323943662</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>34.50106157112526</v>
+      </c>
+      <c r="C21">
         <v>44.01981599433829</v>
-      </c>
-      <c r="C21">
-        <v>34.50106157112526</v>
       </c>
       <c r="D21">
         <v>2.271704180064309</v>
       </c>
       <c r="E21">
-        <v>24.65807730426165</v>
+        <v>19.32606541129832</v>
       </c>
       <c r="F21">
         <v>56.01585728444005</v>
       </c>
       <c r="G21">
-        <v>19.32606541129832</v>
+        <v>24.65807730426165</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>26.89030883919063</v>
+      </c>
+      <c r="C22">
         <v>37.6038338658147</v>
-      </c>
-      <c r="C22">
-        <v>26.89030883919063</v>
       </c>
       <c r="D22">
         <v>2.659303313508921</v>
       </c>
       <c r="E22">
-        <v>22.86028745306228</v>
+        <v>16.34727437524278</v>
       </c>
       <c r="F22">
         <v>60.79243817169494</v>
       </c>
       <c r="G22">
-        <v>16.34727437524278</v>
+        <v>22.86028745306228</v>
       </c>
     </row>
   </sheetData>
